--- a/config/templates/game_config.xlsx
+++ b/config/templates/game_config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project\GodotProject\roguelike-demo\config\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D65A187-39C1-417B-955E-E1CEB2FED2DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C39178E-00AD-4088-91CD-2C1D608360F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="78">
+  <si>
+    <t>说明</t>
+  </si>
+  <si>
+    <t>hp=生命 atk=攻击 chaseSpeed=追踪速度 attackCooldown=攻击间隔(接触伤害冷却) expValue=经验值 isBoss=是否Boss | 攻击范围=CollisionShape2D尺寸，无attackRange字段</t>
+  </si>
   <si>
     <t>id</t>
   </si>
@@ -59,6 +65,9 @@
     <t>野人</t>
   </si>
   <si>
+    <t>atk=伤害 orbitRadius=轨道半径 orbitSpeed=转速 knockbackStrength=击退力</t>
+  </si>
+  <si>
     <t>orbitRadius</t>
   </si>
   <si>
@@ -98,6 +107,9 @@
     <t>飞刀</t>
   </si>
   <si>
+    <t>hp=生命 atk=攻击(武器提供) moveSpeed=移速 weaponSpinSpeed=武器转速 | 开局写入ValueHub，对局内增益系统可动态修改</t>
+  </si>
+  <si>
     <t>moveSpeed</t>
   </si>
   <si>
@@ -110,6 +122,9 @@
     <t>剑客</t>
   </si>
   <si>
+    <t>expRequired=升到下一级所需经验（独立，非累计）</t>
+  </si>
+  <si>
     <t>expRequired</t>
   </si>
   <si>
@@ -143,118 +158,7 @@
     <t>Lv.5</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>Lv.6</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>Lv.7</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>Lv.8</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>Lv.9</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>Lv.10</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>Lv.11</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>Lv.12</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>Lv.13</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>Lv.14</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>Lv.15</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>Lv.16</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>Lv.17</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>Lv.18</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>Lv.19</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>Lv.20</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>Lv.21</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>Lv.22</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>Lv.23</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>Lv.24</t>
+    <t>id=技能标识 name=名称 desc=描述(%s替换数值) effectVar=作用变量 values=各级数值(逗号分隔) type=add/*%/magnet</t>
   </si>
   <si>
     <t>desc</t>
@@ -278,6 +182,9 @@
     <t>可以额外增加%s生命值</t>
   </si>
   <si>
+    <t>10,30,50,80,100</t>
+  </si>
+  <si>
     <t>*%</t>
   </si>
   <si>
@@ -311,25 +218,13 @@
     <t>add</t>
   </si>
   <si>
-    <t>godspeed</t>
-  </si>
-  <si>
-    <t>神速</t>
-  </si>
-  <si>
-    <t>移动速度增加%s</t>
-  </si>
-  <si>
     <t>magnet</t>
   </si>
   <si>
     <t>吸铁石</t>
   </si>
   <si>
-    <t>增加%s吸引经验的范围</t>
-  </si>
-  <si>
-    <t>magnetRange</t>
+    <t>脉冲吸取%s范围内全部经验</t>
   </si>
   <si>
     <t>enlarge</t>
@@ -344,19 +239,20 @@
     <t>weaponScale</t>
   </si>
   <si>
-    <t>10,30,50,80,100</t>
+    <t>damage</t>
+  </si>
+  <si>
+    <t>增伤</t>
+  </si>
+  <si>
+    <t>weaponAtk</t>
+  </si>
+  <si>
+    <t>250:8,280:7,320:6,370:5,430:4,500:3,580:2,700:1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>30,50,80,100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>damage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>增伤</t>
+    <t>5,10,15,20,25,30,40,50,60</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -364,7 +260,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>*%</t>
+    <t>3,5,8,10,20</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -713,44 +609,52 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:I3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -782,35 +686,47 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:F7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="42" customWidth="1"/>
+  </cols>
   <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -827,30 +743,30 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4">
         <v>100</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="F4">
-        <v>300</v>
+        <v>800</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -867,10 +783,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -887,10 +803,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -913,38 +829,46 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A2:G3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>27</v>
+      </c>
+    </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C3">
         <v>30</v>
@@ -970,282 +894,81 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A2:C26"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>32</v>
+      </c>
+    </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C5">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C6">
-        <v>30</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C7">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11">
         <v>300</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>49</v>
-      </c>
-      <c r="B13" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>55</v>
-      </c>
-      <c r="B16" t="s">
-        <v>56</v>
-      </c>
-      <c r="C16">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>57</v>
-      </c>
-      <c r="B17" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B18" t="s">
-        <v>60</v>
-      </c>
-      <c r="C18">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>61</v>
-      </c>
-      <c r="B19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C19">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>63</v>
-      </c>
-      <c r="B20" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>65</v>
-      </c>
-      <c r="B21" t="s">
-        <v>66</v>
-      </c>
-      <c r="C21">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>67</v>
-      </c>
-      <c r="B22" t="s">
-        <v>68</v>
-      </c>
-      <c r="C22">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>69</v>
-      </c>
-      <c r="B23" t="s">
-        <v>70</v>
-      </c>
-      <c r="C23">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>71</v>
-      </c>
-      <c r="B24" t="s">
-        <v>72</v>
-      </c>
-      <c r="C24">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>73</v>
-      </c>
-      <c r="B25" t="s">
-        <v>74</v>
-      </c>
-      <c r="C25">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>75</v>
-      </c>
-      <c r="B26" t="s">
-        <v>76</v>
-      </c>
-      <c r="C26">
-        <v>1000</v>
       </c>
     </row>
   </sheetData>
@@ -1256,167 +979,160 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A2:F9"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="6" width="18.453125" customWidth="1"/>
+    <col min="1" max="4" width="24.26953125" customWidth="1"/>
+    <col min="5" max="5" width="62.54296875" customWidth="1"/>
+    <col min="6" max="6" width="24.26953125" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>44</v>
+      </c>
+    </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="F2" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>107</v>
+        <v>52</v>
       </c>
       <c r="F3" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="E4" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="F4" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="E5" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>94</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6">
-        <v>20</v>
+        <v>64</v>
+      </c>
+      <c r="E6" t="s">
+        <v>74</v>
       </c>
       <c r="F6" t="s">
-        <v>94</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B7" t="s">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="E7" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="F7" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="E8" s="1">
         <v>50100</v>
       </c>
       <c r="F8" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>108</v>
-      </c>
-      <c r="B9" t="s">
-        <v>109</v>
-      </c>
-      <c r="C9" t="s">
-        <v>110</v>
-      </c>
-      <c r="E9" s="1">
-        <v>50100</v>
-      </c>
-      <c r="F9" t="s">
-        <v>111</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
